--- a/models/6971_DCF_Model_20260906.xlsx
+++ b/models/6971_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C34095-BE8D-45BF-B6B4-2FC910CDD81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A0CAD8-E0F7-40A0-9FA1-0012EDA244A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
     <t>Current Price</t>
   </si>
   <si>
-    <t>Target Price (コアDCF + 非連結投資価値（政策保有株式＋持分法、税引後）)</t>
+    <t>Target Price (コアDCF[フロア適用] + 非連結投資価値（政策保有株式＋持分法、税引後）)</t>
   </si>
   <si>
     <t>Recommendation</t>
@@ -87,22 +87,22 @@
     <t>DCF - Exit Multiple</t>
   </si>
   <si>
-    <t>コアDCF 1株値（フロア規則: 負または不成立なら 0）</t>
+    <t>Comps - EV/EBITDA Median [参考・Target不算入]（型F: EV倍率は持分法混在で歪むため不使用）</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Comps - PER Median [参考・Target不算入]</t>
+  </si>
+  <si>
+    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外） ■【型F: 持分法主導】コア営業利益 = 売上総利益 − 販売費及び一般管理費 で定義し、持分法投資損益・受取配当金・金融損益・投資損益をコアから除外している。除外した持分法投資の価値は上の別途加算行で加算する（二重計上なし）。持分法投資価値の算定方式は 'book_value'、詳細は Equity Method Value シート。Comps は EV 倍率が持分法混在で歪むため PER/PBR を参照とする。</t>
+  </si>
+  <si>
+    <t>DCF Valuation Range (PGM - Exit)</t>
   </si>
   <si>
     <t>非連結投資価値（政策保有株式＋持分法、税引後） [1株・別途加算]</t>
-  </si>
-  <si>
-    <t>Comps - EV/EBITDA Median [参考・Target不算入]（型F: EV倍率は持分法混在で歪むため不使用）</t>
-  </si>
-  <si>
-    <t>Comps - PER Median [参考・Target不算入]</t>
-  </si>
-  <si>
-    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外） ■【型F: 持分法主導】コア営業利益 = 売上総利益 − 販売費及び一般管理費 で定義し、持分法投資損益・受取配当金・金融損益・投資損益をコアから除外している。除外した持分法投資の価値は上の別途加算行で加算する（二重計上なし）。持分法投資価値の算定方式は 'book_value'、詳細は Equity Method Value シート。Comps は EV 倍率が持分法混在で歪むため PER/PBR を参照とする。</t>
-  </si>
-  <si>
-    <t>DCF Valuation Range (PGM - Exit)</t>
   </si>
   <si>
     <t>Key Investment Thesis</t>
@@ -763,7 +763,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-07 12:20, template rev 6045157</t>
+    <t>Generated by pipeline on 2026-09-07 13:12, template rev 1e927a2</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -979,7 +979,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-07 12:20:05</t>
+    <t>2026-09-07 13:12:25</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1048,7 +1048,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>6045157</t>
+    <t>1e927a2</t>
   </si>
   <si>
     <t>ticker</t>
@@ -1370,7 +1370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1429,7 +1429,6 @@
     <xf numFmtId="179" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1747,7 +1746,7 @@
   <sheetPr>
     <tabColor rgb="FF003366"/>
   </sheetPr>
-  <dimension ref="B1:E33"/>
+  <dimension ref="B1:E31"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -1756,19 +1755,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
     </row>
     <row r="3" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
     </row>
     <row r="4" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
@@ -1812,7 +1811,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <f>C18+C19</f>
+        <f>MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22</f>
         <v>2143</v>
       </c>
     </row>
@@ -1878,100 +1877,98 @@
         <v>-0.57265201256066234</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="44">
-        <f>MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))</f>
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="4" t="s">
+      <c r="C18" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="45">
+      <c r="D18" s="7" t="str">
+        <f>IF(ISNUMBER(C18),(C18-C9)/C9,"N/A")</f>
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="11">
+        <f>'Comps Analysis'!C28</f>
+        <v>3211</v>
+      </c>
+      <c r="D19" s="7">
+        <f>IF(ISNUMBER(C19),(C19-C9)/C9,"N/A")</f>
+        <v>-8.3357122466457323E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+    </row>
+    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="6" t="str">
+        <f>IF(COUNT(C16:C17)=0,"N/A",MIN(C16:C17)&amp;" - "&amp;MAX(C16:C17))</f>
+        <v>732 - 1497</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+      <c r="B22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="44">
         <f>'Equity Method Value'!C12</f>
         <v>1028</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-    </row>
-    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="11">
-        <f>'Comps Analysis'!C28</f>
-        <v>3211</v>
-      </c>
-      <c r="D21" s="7">
-        <f>IF(ISNUMBER(C19),(C19-C9)/C9,"N/A")</f>
-        <v>-0.70653725378247212</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" ht="14" x14ac:dyDescent="0.3">
-      <c r="B22" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
     <row r="23" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="6" t="str">
-        <f>IF(COUNT(C16:C17)=0,"N/A",MIN(C16:C17)&amp;" - "&amp;MAX(C16:C17))</f>
-        <v>732 - 1497</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" ht="14" x14ac:dyDescent="0.3">
-      <c r="B25" s="8" t="s">
+      <c r="B23" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="2:5" ht="14" x14ac:dyDescent="0.3">
-      <c r="B30" s="8" t="s">
+    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5962,16 +5959,16 @@
       </c>
     </row>
     <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="55" t="s">
         <v>232</v>
       </c>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="55"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6533,7 +6530,7 @@
       </c>
     </row>
     <row r="3" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="45" t="s">
         <v>348</v>
       </c>
     </row>
@@ -6543,60 +6540,60 @@
       </c>
     </row>
     <row r="6" spans="2:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="46" t="s">
         <v>350</v>
       </c>
-      <c r="C6" s="48">
+      <c r="C6" s="47">
         <v>1312686</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="46" t="s">
         <v>351</v>
       </c>
-      <c r="C7" s="49">
+      <c r="C7" s="48">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="14" x14ac:dyDescent="0.3">
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="49" t="s">
         <v>352</v>
       </c>
-      <c r="C8" s="51">
+      <c r="C8" s="50">
         <f>C6*C7</f>
         <v>1312686</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="51" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="46" t="s">
         <v>354</v>
       </c>
-      <c r="C11" s="53">
+      <c r="C11" s="52">
         <f>'DCF Model'!C15</f>
         <v>1277527109</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="14" x14ac:dyDescent="0.3">
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="49" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="50">
         <f>ROUND(C8/C11*1000000,0)</f>
         <v>1028</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="45" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="14" x14ac:dyDescent="0.3">
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="45" t="s">
         <v>357</v>
       </c>
     </row>
